--- a/samples/Sample_1_For_UPSC_IAS_Coaching.xlsx
+++ b/samples/Sample_1_For_UPSC_IAS_Coaching.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vihaan Murthy</t>
+          <t>Rahul Verma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Divya Shetty</t>
+          <t>Priya Kumar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vikram Shetty</t>
+          <t>Pranav Bhat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Divya Bhat</t>
+          <t>Tanya Iyer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Devansh Bhat</t>
+          <t>Varun Singh</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diya Kulkarni</t>
+          <t>Pooja Nair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sameer Gowda</t>
+          <t>Karthik Hegde</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Riya Rao</t>
+          <t>Myra Desai</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Varun Bhat</t>
+          <t>Vihaan Rao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shreya Iyer</t>
+          <t>Anjali Desai</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sameer Hegde</t>
+          <t>Reyansh Joshi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pooja Singh</t>
+          <t>Swathi Kulkarni</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pranav Sharma</t>
+          <t>Krishna Desai</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anjali Reddy</t>
+          <t>Shreya Gowda</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Akash Verma</t>
+          <t>Varun Kulkarni</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ananya Kumar</t>
+          <t>Ananya Hegde</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ishaan Singh</t>
+          <t>Varun Reddy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nisha Sharma</t>
+          <t>Swathi Verma</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pranav Iyer</t>
+          <t>Ishaan Joshi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kritika Nair</t>
+          <t>Divya Gowda</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nikhil Iyer</t>
+          <t>Varun Hegde</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tanya Nair</t>
+          <t>Myra Pai</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rahul Reddy</t>
+          <t>Vikram Reddy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tanya Joshi</t>
+          <t>Ananya Bhat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akash Shetty</t>
+          <t>Arjun Hegde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Riya Patel</t>
+          <t>Tanya Joshi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yash Prabhu</t>
+          <t>Krishna Murthy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Divya Singh</t>
+          <t>Anjali Reddy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ishaan Pai</t>
+          <t>Reyansh Iyer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Divya Verma</t>
+          <t>Myra Shetty</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1611,24 +1611,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C2" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F2" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Indian History - Freedom Struggle</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1638,24 +1642,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>192</v>
+        <v>158</v>
       </c>
       <c r="C3" t="n">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="D3" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E3" t="n">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="F3" t="n">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>World History</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1665,26 +1673,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C4" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D4" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E4" t="n">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="F4" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>World History</t>
+          <t>Indian History - Freedom Struggle</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1696,19 +1704,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C5" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D5" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E5" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1718,11 +1726,7 @@
           <t>World History</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1731,24 +1735,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D6" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E6" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Indian Society</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1758,24 +1766,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D7" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Indian Geography</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1785,19 +1797,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1809,7 +1821,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Below expectations — recommend extra classes after school.</t>
         </is>
       </c>
     </row>
@@ -1820,33 +1832,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>World History</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+          <t>Art &amp; Culture</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1855,33 +1863,29 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Indian History - Freedom Struggle</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Serious concern — immediate intervention needed.</t>
-        </is>
-      </c>
+          <t>Indian Society</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1890,31 +1894,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C11" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Indian History - Freedom Struggle</t>
+          <t>Indian Society</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -1925,33 +1929,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Indian Society</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Needs attention — performance has slipped recently.</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1960,24 +1956,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>137</v>
+        <v>99</v>
       </c>
       <c r="C13" t="n">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E13" t="n">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="F13" t="n">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Indian Society</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1987,28 +1987,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C14" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D14" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F14" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Art &amp; Culture</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -2018,31 +2014,31 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>147</v>
+      </c>
+      <c r="C15" t="n">
+        <v>162</v>
+      </c>
+      <c r="D15" t="n">
+        <v>146</v>
+      </c>
+      <c r="E15" t="n">
         <v>163</v>
       </c>
-      <c r="C15" t="n">
-        <v>167</v>
-      </c>
-      <c r="D15" t="n">
-        <v>181</v>
-      </c>
-      <c r="E15" t="n">
-        <v>181</v>
-      </c>
       <c r="F15" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Art &amp; Culture</t>
+          <t>Indian Geography</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -2053,28 +2049,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="C16" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D16" t="n">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E16" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Indian History - Freedom Struggle</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -2084,26 +2076,26 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C17" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D17" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E17" t="n">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Indian Society</t>
+          <t>World History</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2115,24 +2107,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D18" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E18" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Indian Geography</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2142,26 +2138,26 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="D19" t="n">
+        <v>143</v>
+      </c>
+      <c r="E19" t="n">
         <v>123</v>
       </c>
-      <c r="E19" t="n">
-        <v>118</v>
-      </c>
       <c r="F19" t="n">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Indian History - Freedom Struggle</t>
+          <t>Indian Geography</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2173,33 +2169,29 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C20" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>World History</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
-        </is>
-      </c>
+          <t>Art &amp; Culture</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2208,29 +2200,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C21" t="n">
+        <v>68</v>
+      </c>
+      <c r="D21" t="n">
+        <v>71</v>
+      </c>
+      <c r="E21" t="n">
         <v>74</v>
       </c>
-      <c r="D21" t="n">
-        <v>84</v>
-      </c>
-      <c r="E21" t="n">
-        <v>87</v>
-      </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Indian Society</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2239,25 +2231,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C22" t="n">
         <v>56</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Very low scores across the board, please involve parents.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2266,26 +2262,26 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C23" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
+        <v>64</v>
+      </c>
+      <c r="F23" t="n">
         <v>74</v>
       </c>
-      <c r="F23" t="n">
-        <v>66</v>
-      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Indian Society</t>
+          <t>Indian Geography</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2297,19 +2293,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C24" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="D24" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="E24" t="n">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="F24" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2324,28 +2320,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C25" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D25" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F25" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Indian History - Freedom Struggle</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2355,24 +2347,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C26" t="n">
+        <v>192</v>
+      </c>
+      <c r="D26" t="n">
+        <v>181</v>
+      </c>
+      <c r="E26" t="n">
+        <v>186</v>
+      </c>
+      <c r="F26" t="n">
         <v>191</v>
       </c>
-      <c r="D26" t="n">
-        <v>183</v>
-      </c>
-      <c r="E26" t="n">
-        <v>183</v>
-      </c>
-      <c r="F26" t="n">
-        <v>182</v>
-      </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Indian Society</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2382,29 +2378,33 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="C27" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D27" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E27" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="F27" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Indian Geography</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Indian History - Freedom Struggle</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Strong performer, small gains possible with more practice.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2413,29 +2413,29 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>152</v>
+      </c>
+      <c r="C28" t="n">
+        <v>160</v>
+      </c>
+      <c r="D28" t="n">
+        <v>148</v>
+      </c>
+      <c r="E28" t="n">
         <v>162</v>
       </c>
-      <c r="C28" t="n">
+      <c r="F28" t="n">
         <v>163</v>
       </c>
-      <c r="D28" t="n">
-        <v>174</v>
-      </c>
-      <c r="E28" t="n">
-        <v>172</v>
-      </c>
-      <c r="F28" t="n">
-        <v>172</v>
-      </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Indian Geography</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2444,33 +2444,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C29" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D29" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E29" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F29" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Indian Geography</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+          <t>Art &amp; Culture</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2479,26 +2475,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C30" t="n">
         <v>119</v>
       </c>
       <c r="D30" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E30" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="F30" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Indian Geography</t>
+          <t>Indian History - Freedom Struggle</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -2510,25 +2506,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C31" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D31" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E31" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F31" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2609,33 +2609,29 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D2" t="n">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F2" t="n">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Logical Reasoning</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Consistently excellent — ready for tougher challenges.</t>
-        </is>
-      </c>
+          <t>Comprehension</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2644,24 +2640,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="D3" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="F3" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -2671,29 +2671,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C4" t="n">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="D4" t="n">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E4" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F4" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Decision Making</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Logical Reasoning</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2702,33 +2706,29 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C5" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="D5" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="E5" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Logical Reasoning</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+          <t>Comprehension</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2737,26 +2737,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="F6" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Logical Reasoning</t>
+          <t>Data Interpretation</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2768,24 +2768,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D7" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Logical Reasoning</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -2795,29 +2799,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Data Interpretation</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2826,28 +2830,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Logical Reasoning</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2857,24 +2857,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>33</v>
+      </c>
+      <c r="C10" t="n">
+        <v>27</v>
+      </c>
+      <c r="D10" t="n">
         <v>32</v>
       </c>
-      <c r="C10" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10" t="n">
-        <v>37</v>
-      </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Comprehension</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2884,29 +2888,29 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>112</v>
+      </c>
+      <c r="C11" t="n">
         <v>94</v>
       </c>
-      <c r="C11" t="n">
-        <v>98</v>
-      </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E11" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Comprehension</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Great turnaround this term, keep the momentum going!</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2915,33 +2919,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E12" t="n">
+        <v>127</v>
+      </c>
+      <c r="F12" t="n">
         <v>130</v>
       </c>
-      <c r="F12" t="n">
-        <v>120</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Comprehension</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Noticeable drop in performance, please check in at home.</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2950,26 +2946,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="F13" t="n">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
+          <t>Comprehension</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2981,29 +2977,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C14" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D14" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E14" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F14" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Logical Reasoning</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3012,33 +3008,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C15" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E15" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="F15" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3047,24 +3039,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="C16" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="D16" t="n">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E16" t="n">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="F16" t="n">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Data Interpretation</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3074,29 +3070,33 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="C17" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E17" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Logical Reasoning</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3105,26 +3105,26 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C18" t="n">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D18" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E18" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Comprehension</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3136,29 +3136,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D19" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F19" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Logical Reasoning</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3167,26 +3167,26 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>56</v>
+      </c>
+      <c r="C20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
-        <v>58</v>
-      </c>
       <c r="D20" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Logical Reasoning</t>
+          <t>Decision Making</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3198,25 +3198,33 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Comprehension</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3225,29 +3233,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Comprehension</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Serious concern — immediate intervention needed.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3256,19 +3264,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3287,26 +3295,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C24" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D24" t="n">
         <v>135</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F24" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Data Interpretation</t>
+          <t>Logical Reasoning</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3318,33 +3326,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D25" t="n">
+        <v>107</v>
+      </c>
+      <c r="E25" t="n">
+        <v>104</v>
+      </c>
+      <c r="F25" t="n">
         <v>118</v>
       </c>
-      <c r="E25" t="n">
-        <v>110</v>
-      </c>
-      <c r="F25" t="n">
-        <v>111</v>
-      </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Data Interpretation</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3353,19 +3353,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C26" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D26" t="n">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="E26" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="F26" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -3380,26 +3380,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="C27" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D27" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E27" t="n">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F27" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Decision Making</t>
+          <t>Logical Reasoning</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3411,24 +3411,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C28" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D28" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E28" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F28" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Comprehension</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3438,19 +3442,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C29" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="D29" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="E29" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F29" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -3462,7 +3466,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3477,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C30" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D30" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E30" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F30" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3500,29 +3504,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C31" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D31" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E31" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F31" t="n">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Comprehension</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3603,20 +3607,20 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C2" t="n">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="D2" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E2" t="n">
+        <v>176</v>
+      </c>
+      <c r="F2" t="n">
         <v>183</v>
       </c>
-      <c r="F2" t="n">
-        <v>182</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -3627,7 +3631,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
+          <t>Exceptional performance, keep up this standard.</t>
         </is>
       </c>
     </row>
@@ -3638,26 +3642,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C3" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D3" t="n">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="F3" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Governance</t>
+          <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -3669,33 +3673,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C4" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D4" t="n">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="F4" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Essay Writing Practice - Environment</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3704,24 +3700,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C5" t="n">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D5" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="E5" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="F5" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Environment</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -3731,19 +3731,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D6" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F6" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3758,29 +3758,33 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>124</v>
+      </c>
+      <c r="C7" t="n">
         <v>135</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" t="n">
+        <v>112</v>
+      </c>
+      <c r="F7" t="n">
         <v>132</v>
       </c>
-      <c r="D7" t="n">
-        <v>136</v>
-      </c>
-      <c r="E7" t="n">
-        <v>129</v>
-      </c>
-      <c r="F7" t="n">
-        <v>128</v>
-      </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Governance</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Essay Writing Practice - Environment</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3789,33 +3793,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Environment</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+          <t>Essay Writing Practice - Governance</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3824,16 +3824,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F9" t="n">
         <v>77</v>
@@ -3841,16 +3841,8 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Essay Writing Practice - Environment</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3859,19 +3851,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3890,24 +3882,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F11" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Environment</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -3917,19 +3913,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3948,26 +3944,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E13" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13" t="n">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Governance</t>
+          <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -3979,19 +3975,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C14" t="n">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="D14" t="n">
+        <v>186</v>
+      </c>
+      <c r="E14" t="n">
         <v>182</v>
       </c>
-      <c r="E14" t="n">
-        <v>193</v>
-      </c>
       <c r="F14" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -4010,28 +4006,24 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>169</v>
+      </c>
+      <c r="C15" t="n">
+        <v>172</v>
+      </c>
+      <c r="D15" t="n">
+        <v>171</v>
+      </c>
+      <c r="E15" t="n">
+        <v>181</v>
+      </c>
+      <c r="F15" t="n">
         <v>173</v>
       </c>
-      <c r="C15" t="n">
-        <v>160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>174</v>
-      </c>
-      <c r="E15" t="n">
-        <v>160</v>
-      </c>
-      <c r="F15" t="n">
-        <v>174</v>
-      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Essay Writing Practice - Governance</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4041,28 +4033,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C16" t="n">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="D16" t="n">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="E16" t="n">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Essay Writing Practice - Governance</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4072,24 +4060,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C17" t="n">
+        <v>127</v>
+      </c>
+      <c r="D17" t="n">
         <v>126</v>
       </c>
-      <c r="D17" t="n">
-        <v>128</v>
-      </c>
       <c r="E17" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Governance</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4099,31 +4091,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="C18" t="n">
         <v>130</v>
       </c>
       <c r="D18" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="E18" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Governance</t>
+          <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -4134,25 +4126,33 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>110</v>
+      </c>
+      <c r="C19" t="n">
         <v>119</v>
       </c>
-      <c r="C19" t="n">
-        <v>105</v>
-      </c>
       <c r="D19" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E19" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F19" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Governance</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C20" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4192,29 +4192,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C21" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4223,29 +4219,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C22" t="n">
+        <v>73</v>
+      </c>
+      <c r="D22" t="n">
+        <v>72</v>
+      </c>
+      <c r="E22" t="n">
         <v>53</v>
       </c>
-      <c r="D22" t="n">
-        <v>55</v>
-      </c>
-      <c r="E22" t="n">
-        <v>55</v>
-      </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Serious concern — immediate intervention needed.</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4254,19 +4246,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="C23" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D23" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="F23" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -4285,29 +4277,29 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C24" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D24" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Needs attention — performance has slipped recently.</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Governance</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4316,28 +4308,24 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>121</v>
+      </c>
+      <c r="C25" t="n">
+        <v>112</v>
+      </c>
+      <c r="D25" t="n">
+        <v>103</v>
+      </c>
+      <c r="E25" t="n">
+        <v>123</v>
+      </c>
+      <c r="F25" t="n">
         <v>108</v>
       </c>
-      <c r="C25" t="n">
-        <v>116</v>
-      </c>
-      <c r="D25" t="n">
-        <v>109</v>
-      </c>
-      <c r="E25" t="n">
-        <v>117</v>
-      </c>
-      <c r="F25" t="n">
-        <v>110</v>
-      </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Essay Writing Practice - Environment</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -4347,19 +4335,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C26" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D26" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="E26" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="F26" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4369,11 +4357,7 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4382,29 +4366,33 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C27" t="n">
+        <v>167</v>
+      </c>
+      <c r="D27" t="n">
+        <v>157</v>
+      </c>
+      <c r="E27" t="n">
+        <v>160</v>
+      </c>
+      <c r="F27" t="n">
         <v>170</v>
       </c>
-      <c r="D27" t="n">
-        <v>174</v>
-      </c>
-      <c r="E27" t="n">
-        <v>166</v>
-      </c>
-      <c r="F27" t="n">
-        <v>178</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Governance</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Essay Writing Practice - Environment</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4413,16 +4401,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C28" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D28" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E28" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F28" t="n">
         <v>165</v>
@@ -4430,12 +4418,12 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Environment</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4444,33 +4432,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C29" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D29" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E29" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="F29" t="n">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Essay Writing Practice - Environment</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+          <t>Essay Writing Practice - Governance</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4479,33 +4463,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C30" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D30" t="n">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E30" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F30" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Essay Writing Practice - Environment</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4514,25 +4490,33 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C31" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D31" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="E31" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F31" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Essay Writing Practice - Environment</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4613,26 +4597,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C2" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D2" t="n">
+        <v>186</v>
+      </c>
+      <c r="E2" t="n">
+        <v>187</v>
+      </c>
+      <c r="F2" t="n">
         <v>179</v>
       </c>
-      <c r="E2" t="n">
-        <v>184</v>
-      </c>
-      <c r="F2" t="n">
-        <v>196</v>
-      </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Optional Paper 1 Topics</t>
+          <t>Optional Paper 2 Topics</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4648,19 +4632,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C3" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D3" t="n">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4672,7 +4656,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -4683,31 +4667,31 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>163</v>
+      </c>
+      <c r="C4" t="n">
+        <v>170</v>
+      </c>
+      <c r="D4" t="n">
         <v>158</v>
       </c>
-      <c r="C4" t="n">
-        <v>155</v>
-      </c>
-      <c r="D4" t="n">
-        <v>171</v>
-      </c>
       <c r="E4" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Optional Paper 2 Topics</t>
+          <t>Optional Paper 1 Topics</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -4718,31 +4702,31 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>118</v>
+      </c>
+      <c r="C5" t="n">
+        <v>106</v>
+      </c>
+      <c r="D5" t="n">
+        <v>118</v>
+      </c>
+      <c r="E5" t="n">
+        <v>107</v>
+      </c>
+      <c r="F5" t="n">
         <v>119</v>
       </c>
-      <c r="C5" t="n">
-        <v>137</v>
-      </c>
-      <c r="D5" t="n">
-        <v>132</v>
-      </c>
-      <c r="E5" t="n">
-        <v>131</v>
-      </c>
-      <c r="F5" t="n">
-        <v>128</v>
-      </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Optional Paper 1 Topics</t>
+          <t>Optional Paper 2 Topics</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -4753,31 +4737,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="C6" t="n">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="D6" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Optional Paper 2 Topics</t>
+          <t>Optional Paper 1 Topics</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -4788,31 +4772,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="E7" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="F7" t="n">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Optional Paper 2 Topics</t>
+          <t>Optional Paper 1 Topics</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -4823,19 +4807,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4847,7 +4831,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -4858,27 +4842,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Optional Paper 1 Topics</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -4889,19 +4877,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4924,31 +4912,27 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E11" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="F11" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Optional Paper 1 Topics</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Encouraging progress, on the right track now.</t>
         </is>
       </c>
     </row>
@@ -4959,31 +4943,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Optional Paper 1 Topics</t>
+          <t>Optional Paper 2 Topics</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Was doing well earlier, something seems to be affecting focus now.</t>
+          <t>Noticeable drop in performance, please check in at home.</t>
         </is>
       </c>
     </row>
@@ -4994,31 +4978,27 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Optional Paper 2 Topics</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
+          <t>Ups and downs need to be understood — talk to student directly.</t>
         </is>
       </c>
     </row>
@@ -5029,19 +5009,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C14" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D14" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E14" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F14" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5060,19 +5040,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C15" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E15" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5095,19 +5075,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="C16" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="D16" t="n">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="E16" t="n">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="F16" t="n">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5119,7 +5099,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -5130,28 +5110,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C17" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D17" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Optional Paper 1 Topics</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5165,27 +5141,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C18" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D18" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E18" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F18" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Optional Paper 2 Topics</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5196,19 +5176,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="C19" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5220,7 +5200,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -5231,19 +5211,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" t="n">
         <v>81</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -5255,7 +5235,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Below expectations — recommend extra classes after school.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -5266,31 +5246,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C21" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F21" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Optional Paper 1 Topics</t>
+          <t>Optional Paper 2 Topics</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Finding it difficult to keep pace, needs individual attention.</t>
+          <t>Struggling with fundamentals, needs remedial sessions.</t>
         </is>
       </c>
     </row>
@@ -5301,24 +5281,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C22" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D22" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E22" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Optional Paper 1 Topics</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>Needs urgent academic support, at risk of failing.</t>
@@ -5332,31 +5316,27 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="C23" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="D23" t="n">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E23" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="F23" t="n">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Optional Paper 1 Topics</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -5367,27 +5347,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Optional Paper 1 Topics</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Needs attention — performance has slipped recently.</t>
+          <t>Was doing well earlier, something seems to be affecting focus now.</t>
         </is>
       </c>
     </row>
@@ -5398,24 +5382,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E25" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="F25" t="n">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Optional Paper 2 Topics</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Inconsistent results — strong in some tests, weak in others.</t>
@@ -5432,28 +5420,28 @@
         <v>200</v>
       </c>
       <c r="C26" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D26" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E26" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F26" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Optional Paper 1 Topics</t>
+          <t>Optional Paper 2 Topics</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Exceptional performance, keep up this standard.</t>
+          <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
         </is>
       </c>
     </row>
@@ -5464,19 +5452,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="C27" t="n">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D27" t="n">
         <v>167</v>
       </c>
       <c r="E27" t="n">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="F27" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5484,7 +5472,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -5495,16 +5483,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C28" t="n">
+        <v>175</v>
+      </c>
+      <c r="D28" t="n">
         <v>162</v>
       </c>
-      <c r="D28" t="n">
-        <v>164</v>
-      </c>
       <c r="E28" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F28" t="n">
         <v>176</v>
@@ -5514,7 +5502,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Optional Paper 2 Topics</t>
+          <t>Optional Paper 1 Topics</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -5530,31 +5518,27 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C29" t="n">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="E29" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F29" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Optional Paper 2 Topics</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5565,19 +5549,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C30" t="n">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="D30" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="E30" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F30" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5589,7 +5573,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5600,16 +5584,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C31" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D31" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="E31" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F31" t="n">
         <v>128</v>
@@ -5617,14 +5601,10 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Optional Paper 1 Topics</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>

--- a/samples/Sample_1_For_UPSC_IAS_Coaching.xlsx
+++ b/samples/Sample_1_For_UPSC_IAS_Coaching.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prelims Mock 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prelims Mock 2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mains Mock 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mains Mock 2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch2026-Prelims Mock 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch2026-Prelims Mock 2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch2026-Mains Mock 1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch2026-Mains Mock 2" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -525,7 +525,6 @@
           <t>Section</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -633,7 +632,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prelims Mock 1</t>
+          <t>Batch2026-Prelims Mock 1</t>
         </is>
       </c>
     </row>
@@ -702,7 +701,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Prelims Mock 2</t>
+          <t>Batch2026-Prelims Mock 2</t>
         </is>
       </c>
     </row>
@@ -771,7 +770,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mains Mock 1</t>
+          <t>Batch2026-Mains Mock 1</t>
         </is>
       </c>
     </row>
@@ -840,7 +839,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mains Mock 2</t>
+          <t>Batch2026-Mains Mock 2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1632,6 @@
           <t>Indian History - Freedom Struggle</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1664,7 +1662,6 @@
           <t>World History</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1695,7 +1692,6 @@
           <t>Indian History - Freedom Struggle</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1726,7 +1722,6 @@
           <t>World History</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1757,7 +1752,6 @@
           <t>Indian Society</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1788,7 +1782,6 @@
           <t>Indian Geography</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1854,7 +1847,6 @@
           <t>Art &amp; Culture</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1885,7 +1877,6 @@
           <t>Indian Society</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1946,8 +1937,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1978,7 +1967,6 @@
           <t>Indian Society</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2004,8 +1992,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2066,8 +2052,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2098,7 +2082,6 @@
           <t>World History</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2129,7 +2112,6 @@
           <t>Indian Geography</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2160,7 +2142,6 @@
           <t>Indian Geography</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2191,7 +2172,6 @@
           <t>Art &amp; Culture</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2222,7 +2202,6 @@
           <t>Indian Society</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2248,7 +2227,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Very low scores across the board, please involve parents.</t>
@@ -2284,7 +2262,6 @@
           <t>Indian Geography</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2310,8 +2287,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2337,8 +2312,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2369,7 +2342,6 @@
           <t>Indian Society</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2430,7 +2402,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Solid understanding, encourage attempting harder problems.</t>
@@ -2466,7 +2437,6 @@
           <t>Art &amp; Culture</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2497,7 +2467,6 @@
           <t>Indian History - Freedom Struggle</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2523,7 +2492,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -2631,7 +2599,6 @@
           <t>Comprehension</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2662,7 +2629,6 @@
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2728,7 +2694,6 @@
           <t>Comprehension</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2759,7 +2724,6 @@
           <t>Data Interpretation</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2790,7 +2754,6 @@
           <t>Logical Reasoning</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2816,7 +2779,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -2847,8 +2809,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2879,7 +2839,6 @@
           <t>Comprehension</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2905,7 +2864,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -2936,8 +2894,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2968,7 +2924,6 @@
           <t>Comprehension</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2994,7 +2949,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
@@ -3030,7 +2984,6 @@
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3061,7 +3014,6 @@
           <t>Data Interpretation</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3127,7 +3079,6 @@
           <t>Comprehension</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3158,7 +3109,6 @@
           <t>Logical Reasoning</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3189,7 +3139,6 @@
           <t>Decision Making</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3250,7 +3199,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Serious concern — immediate intervention needed.</t>
@@ -3286,7 +3234,6 @@
           <t>Data Interpretation</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3317,7 +3264,6 @@
           <t>Logical Reasoning</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3343,8 +3289,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3370,8 +3314,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3402,7 +3344,6 @@
           <t>Logical Reasoning</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3433,7 +3374,6 @@
           <t>Comprehension</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3494,8 +3434,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3521,7 +3459,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -3664,7 +3601,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3690,8 +3626,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3722,7 +3656,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3748,8 +3681,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3815,7 +3746,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3841,8 +3771,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3873,7 +3801,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3904,7 +3831,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3935,7 +3861,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3966,7 +3891,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3997,7 +3921,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4023,8 +3946,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4050,8 +3971,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4082,7 +4001,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4183,7 +4101,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4209,8 +4126,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4236,8 +4151,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4268,7 +4181,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4299,7 +4211,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4325,8 +4236,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4357,7 +4266,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4423,7 +4331,6 @@
           <t>Essay Writing Practice - Environment</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4454,7 +4361,6 @@
           <t>Essay Writing Practice - Governance</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4480,8 +4386,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4929,7 +4833,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Encouraging progress, on the right track now.</t>
@@ -4995,7 +4898,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Ups and downs need to be understood — talk to student directly.</t>
@@ -5026,7 +4928,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Exceptional performance, keep up this standard.</t>
@@ -5127,7 +5028,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5333,7 +5233,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -5469,7 +5368,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Strong performer, small gains possible with more practice.</t>
@@ -5535,7 +5433,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -5601,7 +5498,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
